--- a/school_surveys/016_parent_involvement_survey--school_surveys.xlsx
+++ b/school_surveys/016_parent_involvement_survey--school_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -964,8 +964,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,12 +993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'never',_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Never', 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'monthly',_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Monthly', 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'weekly',_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Weekly', 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'daily',_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Daily', 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'email',_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Email', 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'phone',_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Phone', 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'in-person',_'label':_'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'In-person', 'label': 'In-person'}</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
